--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486260_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486260_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9104</v>
+        <v>4.7121</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2333</v>
+        <v>5.035</v>
       </c>
       <c r="F2" t="n">
         <v>-0.3229</v>
@@ -610,10 +610,10 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>0.137</v>
+        <v>-0.0613</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5312</v>
+        <v>0.3329</v>
       </c>
       <c r="U2" t="n">
         <v>-0.3942</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0685</v>
+        <v>2.0318</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8538</v>
+        <v>0.848</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2147</v>
+        <v>1.1838</v>
       </c>
       <c r="G3" t="n">
         <v>2.195</v>
@@ -688,13 +688,13 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>0.656</v>
+        <v>-0.3806</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3447</v>
+        <v>0.3389</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6887</v>
+        <v>-0.7195</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3118</v>
+        <v>1.9526</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0867</v>
+        <v>2.82</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7749</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>1.447</v>
@@ -766,13 +766,13 @@
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6577</v>
+        <v>-1.0169</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5997</v>
+        <v>0.3329</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2573</v>
+        <v>-1.3498</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CARRALERO MARTIN</t>
+          <t>M. FRIERSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9572000000000001</v>
+        <v>1.2651</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7319</v>
+        <v>1.3445</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2253</v>
+        <v>-0.0793</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7501</v>
+        <v>1.0012</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2529</v>
+        <v>0.5565</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4972</v>
+        <v>0.4447</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3073</v>
+        <v>0.7104</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7702</v>
+        <v>0.4594</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5371</v>
+        <v>0.251</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5572</v>
+        <v>0.2907</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5173</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0399</v>
+        <v>0.1936</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2501</v>
+        <v>-1.1711</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5997</v>
+        <v>-0.1262</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3496</v>
+        <v>-1.0449</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3904</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3904</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. FRIERSON</t>
+          <t>J. CARRALERO MARTIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5214</v>
+        <v>0.9448</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7857</v>
+        <v>0.6886</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2643</v>
+        <v>0.2562</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0012</v>
+        <v>1.7501</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5565</v>
+        <v>1.2529</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4447</v>
+        <v>0.4972</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7104</v>
+        <v>2.3073</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4594</v>
+        <v>1.7702</v>
       </c>
       <c r="L6" t="n">
-        <v>0.251</v>
+        <v>0.5371</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2907</v>
+        <v>-0.5572</v>
       </c>
       <c r="N6" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.5173</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1936</v>
+        <v>-0.0399</v>
       </c>
       <c r="P6" t="n">
-        <v>0.87</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R6" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.9148</v>
+        <v>0.2376</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.5564</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2298</v>
+        <v>-0.3188</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.3904</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1952</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2889</v>
+        <v>0.3505</v>
       </c>
       <c r="E7" t="n">
         <v>-0.0502</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3391</v>
+        <v>0.4008</v>
       </c>
       <c r="G7" t="n">
         <v>0.3163</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0274</v>
+        <v>0.0342</v>
       </c>
       <c r="T7" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0411</v>
+        <v>0.1027</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. URDIAIN LABAYEN</t>
+          <t>M. N´GUESSAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8656</v>
+        <v>-1.2247</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7258</v>
+        <v>-1.1666</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1398</v>
+        <v>-0.0581</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0263</v>
+        <v>0.8375</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6264</v>
+        <v>-0.0367</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6</v>
+        <v>0.8741</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7811</v>
+        <v>0.9141</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8942</v>
+        <v>0.1492</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1131</v>
+        <v>0.765</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7548</v>
+        <v>-0.0767</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2679</v>
+        <v>-0.1858</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4869</v>
+        <v>0.1091</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.87</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1081</v>
+        <v>-0.7348</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6682</v>
+        <v>-0.1009</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4399</v>
+        <v>-0.6339</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. N´GUESSAN</t>
+          <t>A. URDIAIN LABAYEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8019</v>
+        <v>-1.3413</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6822</v>
+        <v>-0.9241</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1197</v>
+        <v>-0.4172</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8375</v>
+        <v>0.0263</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0367</v>
+        <v>0.6264</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8741</v>
+        <v>-0.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9141</v>
+        <v>0.7811</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1492</v>
+        <v>0.8942</v>
       </c>
       <c r="L9" t="n">
-        <v>0.765</v>
+        <v>-0.1131</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0767</v>
+        <v>-0.7548</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1858</v>
+        <v>-0.2679</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1091</v>
+        <v>-0.4869</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5225</v>
+        <v>-0.87</v>
       </c>
       <c r="Q9" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.312</v>
+        <v>0.6324</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6165</v>
+        <v>0.4699</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6956</v>
+        <v>0.1625</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1952</v>
+        <v>-1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8385</v>
+        <v>-1.4656</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0611</v>
+        <v>-0.6573</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7774</v>
+        <v>-0.8082</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8193</v>
@@ -1234,13 +1234,13 @@
         <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6717</v>
+        <v>-1.2987</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6165</v>
+        <v>-0.2127</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0552</v>
+        <v>-1.086</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2107</v>
+        <v>-1.9756</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6625</v>
+        <v>-2.5507</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4518</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2859</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4898</v>
+        <v>-0.2548</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.274</v>
+        <v>-0.1622</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2158</v>
+        <v>-0.0925</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.7759</v>
+        <v>-6.5446</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.2002</v>
+        <v>-6.7531</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4243</v>
+        <v>0.2085</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9238</v>
@@ -1390,13 +1390,13 @@
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.372</v>
+        <v>-1.1407</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.3064</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6185</v>
+        <v>-0.8343</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.9465</v>
+        <v>-7.401</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.0833</v>
+        <v>-4.7228</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.8631</v>
+        <v>-2.6782</v>
       </c>
       <c r="G13" t="n">
         <v>-4.345</v>
@@ -1468,13 +1468,13 @@
         <v>1.0875</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6662</v>
+        <v>-0.1208</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.3521</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6578000000000001</v>
+        <v>-0.4729</v>
       </c>
       <c r="V13" t="n">
         <v>-0.7602</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.3809</v>
+        <v>-8.695899999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.773899999999999</v>
+        <v>-6.088700000000002</v>
       </c>
       <c r="F14" t="n">
         <v>-2.6069</v>
       </c>
       <c r="G14" t="n">
-        <v>4.820500000000002</v>
+        <v>4.8205</v>
       </c>
       <c r="H14" t="n">
         <v>-0.5941999999999998</v>
@@ -1522,7 +1522,7 @@
         <v>9.6472</v>
       </c>
       <c r="K14" t="n">
-        <v>3.833699999999999</v>
+        <v>3.833699999999998</v>
       </c>
       <c r="L14" t="n">
         <v>5.813300000000001</v>
@@ -1531,10 +1531,10 @@
         <v>-4.8269</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.4281</v>
+        <v>-4.428100000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3987999999999999</v>
+        <v>-0.3988</v>
       </c>
       <c r="P14" t="n">
         <v>-6.5252</v>
@@ -1546,13 +1546,13 @@
         <v>11.9625</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.9604</v>
+        <v>-5.2755</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7211000000000004</v>
+        <v>1.4062</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.6815</v>
+        <v>-6.6816</v>
       </c>
       <c r="V14" t="n">
         <v>-1.7156</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9914</v>
+        <v>4.8353</v>
       </c>
       <c r="E15" t="n">
-        <v>2.787</v>
+        <v>3.5693</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2044</v>
+        <v>1.266</v>
       </c>
       <c r="G15" t="n">
         <v>3.9623</v>
@@ -1624,13 +1624,13 @@
         <v>2.6101</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1884</v>
+        <v>0.6555</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2379</v>
+        <v>0.5444</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0495</v>
+        <v>0.1111</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>J. GONZALEZ CALVO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8235</v>
+        <v>2.71</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1106</v>
+        <v>1.1598</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7129</v>
+        <v>1.5501</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9738</v>
+        <v>0.2351</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4424</v>
+        <v>-0.0852</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4686</v>
+        <v>0.3203</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7971</v>
+        <v>-0.2071</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7588</v>
+        <v>-0.3983</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0382</v>
+        <v>0.1912</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8233</v>
+        <v>0.4422</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3164</v>
+        <v>0.3131</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5068</v>
+        <v>0.1291</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9576</v>
+        <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0243</v>
+        <v>1.4096</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4456</v>
+        <v>1.1717</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5786</v>
+        <v>0.2379</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7395</v>
+        <v>0.1952</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7395</v>
+        <v>0.1952</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7669</v>
+        <v>2.0001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.074</v>
+        <v>-0.2613</v>
       </c>
       <c r="F17" t="n">
-        <v>2.693</v>
+        <v>2.2614</v>
       </c>
       <c r="G17" t="n">
         <v>-2.0628</v>
@@ -1780,13 +1780,13 @@
         <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8944</v>
+        <v>2.1276</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9167</v>
+        <v>1.5814</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9777</v>
+        <v>0.5462</v>
       </c>
       <c r="V17" t="n">
         <v>0.1952</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. GONZALEZ CALVO</t>
+          <t>A. KUNKEL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.71</v>
+        <v>1.8934</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1598</v>
+        <v>-0.7991</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5501</v>
+        <v>2.6925</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2351</v>
+        <v>-0.6068</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0852</v>
+        <v>-3.1049</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3203</v>
+        <v>2.4982</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2071</v>
+        <v>-0.6465</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3983</v>
+        <v>-3.269</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1912</v>
+        <v>2.6225</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4422</v>
+        <v>0.0398</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3131</v>
+        <v>0.1641</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1291</v>
+        <v>-0.1243</v>
       </c>
       <c r="P18" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>0.87</v>
+        <v>2.3926</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4096</v>
+        <v>1.1951</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1717</v>
+        <v>0.9349</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2379</v>
+        <v>0.2602</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. VRANKIC</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.905</v>
+        <v>1.5789</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9725</v>
+        <v>0.3283</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0675</v>
+        <v>1.2506</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1399</v>
+        <v>1.9738</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2522</v>
+        <v>2.4424</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8877</v>
+        <v>-0.4686</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6158</v>
+        <v>2.7971</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2317</v>
+        <v>2.7588</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3841</v>
+        <v>0.0382</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7556</v>
+        <v>-0.8233</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4838</v>
+        <v>-0.3164</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2718</v>
+        <v>-0.5068</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0875</v>
+        <v>-0.435</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="R19" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2178</v>
+        <v>0.7796</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5742</v>
+        <v>0.6633</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3564</v>
+        <v>0.1163</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7395</v>
+        <v>-0.7395</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. KUNKEL</t>
+          <t>A. MUÑOZ BORCHERS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0494</v>
+        <v>1.3534</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5814</v>
+        <v>-0.2694</v>
       </c>
       <c r="F20" t="n">
-        <v>2.6308</v>
+        <v>1.6228</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6068</v>
+        <v>-0.6252</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.1049</v>
+        <v>-0.736</v>
       </c>
       <c r="I20" t="n">
-        <v>2.4982</v>
+        <v>0.1108</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6465</v>
+        <v>0.1135</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.269</v>
+        <v>-0.2706</v>
       </c>
       <c r="L20" t="n">
-        <v>2.6225</v>
+        <v>0.3841</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0398</v>
+        <v>-0.7388</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1641</v>
+        <v>-0.4654</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1243</v>
+        <v>-0.2733</v>
       </c>
       <c r="P20" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R20" t="n">
         <v>2.3926</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3511</v>
+        <v>0.6312</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1526</v>
+        <v>0.6621</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1985</v>
+        <v>-0.031</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MUÑOZ BORCHERS</t>
+          <t>J. VRANKIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0374</v>
+        <v>1.246</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4929</v>
+        <v>1.1902</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5304</v>
+        <v>0.0558</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6252</v>
+        <v>-1.1399</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.736</v>
+        <v>-0.2522</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1108</v>
+        <v>-0.8877</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1135</v>
+        <v>0.6158</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2706</v>
+        <v>0.2317</v>
       </c>
       <c r="L21" t="n">
         <v>0.3841</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7388</v>
+        <v>-1.7556</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4654</v>
+        <v>-0.4838</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2733</v>
+        <v>-1.2718</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3926</v>
+        <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3152</v>
+        <v>0.5588</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4386</v>
+        <v>0.7919</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1234</v>
+        <v>-0.2331</v>
       </c>
       <c r="V21" t="n">
-        <v>1.13</v>
+        <v>0.7395</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2052</v>
+        <v>1.0028</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0432</v>
+        <v>0.3784</v>
       </c>
       <c r="F22" t="n">
-        <v>0.162</v>
+        <v>0.6244</v>
       </c>
       <c r="G22" t="n">
         <v>-0.3938</v>
@@ -2170,13 +2170,13 @@
         <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4212</v>
+        <v>0.3764</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2452</v>
+        <v>0.5804</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6663</v>
+        <v>-0.204</v>
       </c>
       <c r="V22" t="n">
         <v>1.8902</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>S. UGOCHUKWU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3135</v>
+        <v>-0.2853</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0708</v>
+        <v>0.2134</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3843</v>
+        <v>-0.4988</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6731</v>
+        <v>-0.7212</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2707</v>
+        <v>-0.3953</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4024</v>
+        <v>-0.3259</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6752</v>
+        <v>0.2622</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6752</v>
+        <v>0.1857</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.0765</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3484</v>
+        <v>-0.9834000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9459</v>
+        <v>-0.581</v>
       </c>
       <c r="O23" t="n">
         <v>-0.4024</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7947</v>
+        <v>-0.4341</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7006</v>
+        <v>-0.2439</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0941</v>
+        <v>-0.1902</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. UGOCHUKWU</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4164</v>
+        <v>-0.7528</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0101</v>
+        <v>-0.1527</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4063</v>
+        <v>-0.6</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7212</v>
+        <v>-0.6731</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3953</v>
+        <v>-0.2707</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3259</v>
+        <v>-0.4024</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2622</v>
+        <v>0.6752</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1857</v>
+        <v>0.6752</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0765</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.9834000000000001</v>
+        <v>-1.3484</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.581</v>
+        <v>-0.9459</v>
       </c>
       <c r="O24" t="n">
         <v>-0.4024</v>
       </c>
       <c r="P24" t="n">
-        <v>0.87</v>
+        <v>-0.435</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R24" t="n">
         <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5652</v>
+        <v>0.3554</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4675</v>
+        <v>0.4771</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0977</v>
+        <v>-0.1217</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>M. RODRIGUEZ BARRIENTOS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.1793</v>
+        <v>-2.9523</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.519</v>
+        <v>-2.0075</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.6603</v>
+        <v>-0.9448</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.5458</v>
+        <v>-2.223</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8852</v>
+        <v>-1.3473</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.6607</v>
+        <v>-0.8757</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-1.6667</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1277</v>
+        <v>-1.3624</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.7068</v>
+        <v>-0.3044</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.9668</v>
+        <v>-0.5563</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.0129</v>
+        <v>0.0151</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9539</v>
+        <v>-0.5714</v>
       </c>
       <c r="P25" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>1.0875</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7432</v>
+        <v>-0.882</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2776</v>
+        <v>-0.536</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0208</v>
+        <v>-0.3461</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.7602</v>
+        <v>-0.9347</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.7602</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ BARRIENTOS</t>
+          <t>T. BORG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.1989</v>
+        <v>-3.2487</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.0075</v>
+        <v>-0.7425</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.1914</v>
+        <v>-2.5062</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.223</v>
+        <v>-2.5458</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.3473</v>
+        <v>-0.8852</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8757</v>
+        <v>-1.6607</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.6667</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.3624</v>
+        <v>0.1277</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.3044</v>
+        <v>-0.7068</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.5563</v>
+        <v>-1.9668</v>
       </c>
       <c r="N26" t="n">
-        <v>0.0151</v>
+        <v>-1.0129</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.5714</v>
+        <v>-0.9539</v>
       </c>
       <c r="P26" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R26" t="n">
         <v>1.0875</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.1286</v>
+        <v>-0.8126</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.536</v>
+        <v>0.0541</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5927</v>
+        <v>-0.8667</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.9347</v>
+        <v>-0.7602</v>
       </c>
       <c r="W26" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.13</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="27">
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>9.380700000000001</v>
+        <v>9.380800000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>2.606999999999999</v>
+        <v>2.6069</v>
       </c>
       <c r="F27" t="n">
-        <v>6.773800000000001</v>
+        <v>6.7738</v>
       </c>
       <c r="G27" t="n">
         <v>-4.820399999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5942999999999996</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="I27" t="n">
         <v>-5.4146</v>
@@ -2536,7 +2536,7 @@
         <v>4.8268</v>
       </c>
       <c r="K27" t="n">
-        <v>4.428099999999999</v>
+        <v>4.4281</v>
       </c>
       <c r="L27" t="n">
         <v>0.3985000000000002</v>
@@ -2548,10 +2548,10 @@
         <v>-3.8337</v>
       </c>
       <c r="O27" t="n">
-        <v>-5.8132</v>
+        <v>-5.813199999999999</v>
       </c>
       <c r="P27" t="n">
-        <v>6.5251</v>
+        <v>6.525100000000001</v>
       </c>
       <c r="Q27" t="n">
         <v>-11.9629</v>
@@ -2563,10 +2563,10 @@
         <v>5.960500000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>6.681399999999998</v>
+        <v>6.6814</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.7209999999999999</v>
+        <v>-0.7211000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>1.7157</v>
